--- a/ICSummary/20250211/PerformanceSummaryJan2025.xlsx
+++ b/ICSummary/20250211/PerformanceSummaryJan2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fa1b30dd86628461/FILE Backup/Kev/PYTHON Projects/AtchisonAnalyticsWebsite/ICSummary/20250211/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="372" documentId="8_{8585333A-8958-49B5-87CD-D3974D5B51CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDB54A74-E467-4DAE-95F0-D1F79D3AE79E}"/>
+  <xr:revisionPtr revIDLastSave="373" documentId="8_{8585333A-8958-49B5-87CD-D3974D5B51CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81C61DDD-705B-48FE-9BCE-E56880E9BDA2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{E02CCEAF-9CFD-4D4D-B2FA-7B81BC99F0F0}"/>
   </bookViews>
@@ -557,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -662,71 +662,64 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1087,15 +1080,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" s="25" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
       <c r="J1" s="32"/>
     </row>
     <row r="4" spans="2:12" s="25" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
@@ -1790,64 +1783,63 @@
     <col min="10" max="10" width="3.42578125" customWidth="1"/>
     <col min="11" max="12" width="18.7109375" customWidth="1"/>
     <col min="13" max="13" width="3.42578125" customWidth="1"/>
-    <col min="14" max="14" width="18.7109375" style="46" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" customWidth="1"/>
+    <col min="14" max="15" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:15" s="25" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="C1" s="40"/>
-      <c r="D1" s="40"/>
-      <c r="E1" s="40"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
       <c r="I1" s="39"/>
       <c r="K1" s="32"/>
-      <c r="N1" s="45"/>
+      <c r="N1" s="32"/>
     </row>
     <row r="4" spans="2:15" s="25" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="D4" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="E4" s="55" t="s">
+      <c r="E4" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="55" t="s">
+      <c r="F4" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="55" t="s">
+      <c r="G4" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="55" t="s">
+      <c r="H4" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="I4" s="56" t="s">
+      <c r="I4" s="50" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="61" t="s">
+      <c r="K4" s="55" t="s">
         <v>29</v>
       </c>
-      <c r="L4" s="62" t="s">
+      <c r="L4" s="56" t="s">
         <v>28</v>
       </c>
-      <c r="N4" s="61" t="s">
+      <c r="N4" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="O4" s="62" t="s">
+      <c r="O4" s="56" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="2:15" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="51" t="s">
         <v>6</v>
       </c>
       <c r="C5" s="3">
@@ -1872,22 +1864,22 @@
         <v>11.73</v>
       </c>
       <c r="J5" s="6"/>
-      <c r="K5" s="42">
+      <c r="K5" s="41">
         <v>7.61</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="40">
         <v>1.1599999999999999</v>
       </c>
       <c r="M5" s="6"/>
-      <c r="N5" s="42">
+      <c r="N5" s="41">
         <v>6.57</v>
       </c>
-      <c r="O5" s="41">
+      <c r="O5" s="40">
         <v>-7.27</v>
       </c>
     </row>
     <row r="6" spans="2:15" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="51" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="8">
@@ -1912,22 +1904,22 @@
         <v>11.57</v>
       </c>
       <c r="J6" s="6"/>
-      <c r="K6" s="47">
+      <c r="K6" s="43">
         <v>6.68</v>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="42">
         <v>0.9</v>
       </c>
       <c r="M6" s="6"/>
-      <c r="N6" s="47">
+      <c r="N6" s="43">
         <v>7.4</v>
       </c>
-      <c r="O6" s="43">
+      <c r="O6" s="42">
         <v>-8.7100000000000009</v>
       </c>
     </row>
     <row r="7" spans="2:15" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="54" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="10">
@@ -1952,7 +1944,7 @@
         <v>9.56</v>
       </c>
       <c r="J7" s="13"/>
-      <c r="K7" s="63">
+      <c r="K7" s="57">
         <v>4.9800000000000004</v>
       </c>
       <c r="L7" s="12">
@@ -1967,7 +1959,7 @@
       </c>
     </row>
     <row r="8" spans="2:15" s="2" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="52" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="14"/>
@@ -1983,10 +1975,9 @@
       <c r="I8" s="16">
         <v>3.38</v>
       </c>
-      <c r="K8" s="64">
+      <c r="K8" s="58">
         <v>4.58</v>
       </c>
-      <c r="N8" s="48"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C9" s="17"/>
@@ -1997,10 +1988,10 @@
       <c r="H9" s="17"/>
       <c r="I9" s="17"/>
       <c r="J9" s="17"/>
-      <c r="K9" s="44"/>
+      <c r="K9" s="17"/>
       <c r="L9" s="17"/>
       <c r="M9" s="17"/>
-      <c r="N9" s="44"/>
+      <c r="N9" s="17"/>
       <c r="O9" s="17"/>
     </row>
     <row r="10" spans="2:15" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
@@ -2029,17 +2020,17 @@
         <v>13.65</v>
       </c>
       <c r="J10" s="6"/>
-      <c r="K10" s="42">
+      <c r="K10" s="41">
         <v>8.92</v>
       </c>
-      <c r="L10" s="41">
+      <c r="L10" s="40">
         <v>1.1399999999999999</v>
       </c>
       <c r="M10" s="6"/>
-      <c r="N10" s="42">
+      <c r="N10" s="41">
         <v>7.81</v>
       </c>
-      <c r="O10" s="41">
+      <c r="O10" s="40">
         <v>-8.4700000000000006</v>
       </c>
     </row>
@@ -2069,17 +2060,17 @@
         <v>13.58</v>
       </c>
       <c r="J11" s="6"/>
-      <c r="K11" s="47">
+      <c r="K11" s="43">
         <v>8.15</v>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="42">
         <v>0.95</v>
       </c>
       <c r="M11" s="6"/>
-      <c r="N11" s="47">
+      <c r="N11" s="43">
         <v>8.58</v>
       </c>
-      <c r="O11" s="43">
+      <c r="O11" s="42">
         <v>-9.82</v>
       </c>
     </row>
@@ -2109,7 +2100,7 @@
         <v>11.8</v>
       </c>
       <c r="J12" s="17"/>
-      <c r="K12" s="63">
+      <c r="K12" s="57">
         <v>6.3</v>
       </c>
       <c r="L12" s="12">
@@ -2144,12 +2135,12 @@
         <v>3.38</v>
       </c>
       <c r="J13" s="13"/>
-      <c r="K13" s="64">
+      <c r="K13" s="58">
         <f>K8</f>
         <v>4.58</v>
       </c>
       <c r="M13" s="13"/>
-      <c r="N13" s="49"/>
+      <c r="N13" s="13"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C14" s="17"/>
@@ -2160,10 +2151,10 @@
       <c r="H14" s="17"/>
       <c r="I14" s="17"/>
       <c r="J14" s="17"/>
-      <c r="K14" s="44"/>
+      <c r="K14" s="17"/>
       <c r="L14" s="17"/>
       <c r="M14" s="17"/>
-      <c r="N14" s="44"/>
+      <c r="N14" s="17"/>
       <c r="O14" s="17"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
@@ -2175,10 +2166,10 @@
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
       <c r="J15" s="17"/>
-      <c r="K15" s="44"/>
+      <c r="K15" s="17"/>
       <c r="L15" s="17"/>
       <c r="M15" s="17"/>
-      <c r="N15" s="44"/>
+      <c r="N15" s="17"/>
       <c r="O15" s="17"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
@@ -2190,54 +2181,54 @@
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
       <c r="J16" s="17"/>
-      <c r="K16" s="44"/>
+      <c r="K16" s="17"/>
       <c r="L16" s="17"/>
       <c r="M16" s="17"/>
-      <c r="N16" s="44"/>
+      <c r="N16" s="17"/>
       <c r="O16" s="17"/>
     </row>
     <row r="17" spans="2:15" s="25" customFormat="1" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="52" t="s">
+      <c r="B17" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="53" t="s">
+      <c r="C17" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="D17" s="54" t="s">
+      <c r="D17" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="E17" s="54" t="s">
+      <c r="E17" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="F17" s="54" t="s">
+      <c r="F17" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="G17" s="54" t="s">
+      <c r="G17" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="55" t="s">
+      <c r="H17" s="49" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="56" t="s">
+      <c r="I17" s="50" t="s">
         <v>26</v>
       </c>
       <c r="J17" s="28"/>
-      <c r="K17" s="50" t="s">
+      <c r="K17" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="L17" s="51" t="s">
+      <c r="L17" s="45" t="s">
         <v>28</v>
       </c>
       <c r="M17" s="28"/>
-      <c r="N17" s="50" t="s">
+      <c r="N17" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="O17" s="51" t="s">
+      <c r="O17" s="45" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="18" spans="2:15" s="1" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="51" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="3">
@@ -2262,22 +2253,22 @@
         <v>13.5</v>
       </c>
       <c r="J18" s="6"/>
-      <c r="K18" s="47">
+      <c r="K18" s="43">
         <v>11.25</v>
       </c>
-      <c r="L18" s="43">
+      <c r="L18" s="42">
         <v>0.86</v>
       </c>
       <c r="M18" s="6"/>
-      <c r="N18" s="47">
+      <c r="N18" s="43">
         <v>13.03</v>
       </c>
-      <c r="O18" s="43">
+      <c r="O18" s="42">
         <v>-12.52</v>
       </c>
     </row>
     <row r="19" spans="2:15" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="52" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="14">
@@ -2319,17 +2310,17 @@
     <row r="20" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
-      <c r="E20" s="44"/>
-      <c r="F20" s="44"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
       <c r="J20" s="17"/>
-      <c r="K20" s="44"/>
-      <c r="L20" s="44"/>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
       <c r="M20" s="17"/>
-      <c r="N20" s="44"/>
-      <c r="O20" s="44"/>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
     </row>
     <row r="21" spans="2:15" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B21" s="29" t="s">
@@ -2357,17 +2348,17 @@
         <v>24.25</v>
       </c>
       <c r="J21" s="17"/>
-      <c r="K21" s="47">
+      <c r="K21" s="43">
         <v>12.61</v>
       </c>
-      <c r="L21" s="43">
+      <c r="L21" s="42">
         <v>1.1399999999999999</v>
       </c>
       <c r="M21" s="17"/>
-      <c r="N21" s="42">
+      <c r="N21" s="41">
         <v>11.11</v>
       </c>
-      <c r="O21" s="43">
+      <c r="O21" s="42">
         <v>-10.79</v>
       </c>
     </row>
@@ -2414,17 +2405,17 @@
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
-      <c r="E23" s="44"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="44"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
       <c r="J23" s="17"/>
-      <c r="K23" s="44"/>
-      <c r="L23" s="44"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="17"/>
       <c r="M23" s="17"/>
-      <c r="N23" s="44"/>
-      <c r="O23" s="44"/>
+      <c r="N23" s="17"/>
+      <c r="O23" s="17"/>
     </row>
     <row r="24" spans="2:15" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B24" s="29" t="s">
@@ -2452,17 +2443,17 @@
         <v>7.29</v>
       </c>
       <c r="J24" s="17"/>
-      <c r="K24" s="47">
+      <c r="K24" s="43">
         <v>2.08</v>
       </c>
-      <c r="L24" s="43">
+      <c r="L24" s="42">
         <v>0.16</v>
       </c>
       <c r="M24" s="17"/>
-      <c r="N24" s="42">
+      <c r="N24" s="41">
         <v>12.91</v>
       </c>
-      <c r="O24" s="43">
+      <c r="O24" s="42">
         <v>-16.190000000000001</v>
       </c>
     </row>
@@ -2509,17 +2500,17 @@
     <row r="26" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="44"/>
-      <c r="G26" s="44"/>
-      <c r="H26" s="44"/>
-      <c r="I26" s="44"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
       <c r="J26" s="17"/>
-      <c r="K26" s="44"/>
-      <c r="L26" s="44"/>
+      <c r="K26" s="17"/>
+      <c r="L26" s="17"/>
       <c r="M26" s="17"/>
-      <c r="N26" s="44"/>
-      <c r="O26" s="44"/>
+      <c r="N26" s="17"/>
+      <c r="O26" s="17"/>
     </row>
     <row r="27" spans="2:15" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B27" s="29" t="s">
@@ -2547,17 +2538,17 @@
         <v>8.7100000000000009</v>
       </c>
       <c r="J27" s="17"/>
-      <c r="K27" s="47">
+      <c r="K27" s="43">
         <v>6.21</v>
       </c>
-      <c r="L27" s="43">
+      <c r="L27" s="42">
         <v>1.6</v>
       </c>
       <c r="M27" s="17"/>
-      <c r="N27" s="42">
+      <c r="N27" s="41">
         <v>3.89</v>
       </c>
-      <c r="O27" s="43">
+      <c r="O27" s="42">
         <v>-3.31</v>
       </c>
     </row>
@@ -2604,17 +2595,17 @@
     <row r="29" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
       <c r="J29" s="17"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="44"/>
+      <c r="K29" s="17"/>
+      <c r="L29" s="17"/>
       <c r="M29" s="17"/>
-      <c r="N29" s="44"/>
-      <c r="O29" s="44"/>
+      <c r="N29" s="17"/>
+      <c r="O29" s="17"/>
     </row>
     <row r="30" spans="2:15" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B30" s="29" t="s">
@@ -2642,17 +2633,17 @@
         <v>3.78</v>
       </c>
       <c r="J30" s="17"/>
-      <c r="K30" s="47">
+      <c r="K30" s="43">
         <v>-0.7</v>
       </c>
-      <c r="L30" s="43">
+      <c r="L30" s="42">
         <v>-0.11</v>
       </c>
       <c r="M30" s="17"/>
-      <c r="N30" s="42">
+      <c r="N30" s="41">
         <v>6.35</v>
       </c>
-      <c r="O30" s="43">
+      <c r="O30" s="42">
         <v>-10.23</v>
       </c>
     </row>
@@ -2699,17 +2690,17 @@
     <row r="32" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="44"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
       <c r="J32" s="17"/>
-      <c r="K32" s="44"/>
-      <c r="L32" s="44"/>
+      <c r="K32" s="17"/>
+      <c r="L32" s="17"/>
       <c r="M32" s="17"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="44"/>
+      <c r="N32" s="17"/>
+      <c r="O32" s="17"/>
     </row>
     <row r="33" spans="2:15" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B33" s="29" t="s">
@@ -2737,17 +2728,17 @@
         <v>6.01</v>
       </c>
       <c r="J33" s="17"/>
-      <c r="K33" s="47">
+      <c r="K33" s="43">
         <v>4.09</v>
       </c>
-      <c r="L33" s="43">
+      <c r="L33" s="42">
         <v>2.54</v>
       </c>
       <c r="M33" s="17"/>
-      <c r="N33" s="42">
+      <c r="N33" s="41">
         <v>1.61</v>
       </c>
-      <c r="O33" s="43">
+      <c r="O33" s="42">
         <v>-2.5</v>
       </c>
     </row>
@@ -2798,7 +2789,7 @@
       <c r="K36" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="N36" s="48"/>
+      <c r="N36" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2806,6 +2797,6 @@
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="67" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="88" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ICSummary/20250211/PerformanceSummaryJan2025.xlsx
+++ b/ICSummary/20250211/PerformanceSummaryJan2025.xlsx
@@ -2799,4 +2799,291 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="8" scale="88" orientation="landscape" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005C6577D0C3AE724BBB504F46D5A19401" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="17afb16e0fbe716d3dcf2481b32b5550">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="df76e320-99cb-4a11-b59f-8bf32867ab70" xmlns:ns3="c0789f30-979e-497b-8344-faefb3987540" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f6d0bb8d4e6a5d6b988ea2ed2503dbb5" ns2:_="" ns3:_="">
+    <xsd:import namespace="df76e320-99cb-4a11-b59f-8bf32867ab70"/>
+    <xsd:import namespace="c0789f30-979e-497b-8344-faefb3987540"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="df76e320-99cb-4a11-b59f-8bf32867ab70" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="21" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2ea5f6a7-5373-4784-9cd5-4ca8be386d98" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="23" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c0789f30-979e-497b-8344-faefb3987540" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="22" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{f1100522-260f-4f17-9a31-47a12622b1e0}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="c0789f30-979e-497b-8344-faefb3987540">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="c0789f30-979e-497b-8344-faefb3987540" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="df76e320-99cb-4a11-b59f-8bf32867ab70">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CE2998BF-E29E-465D-9AD2-F835BD83E4B7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8DC8BE2F-706D-4AB4-BA2F-194F528530F4}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C295ECCD-33EB-4BEA-B54A-8EFAD0FE5E7A}"/>
 </file>